--- a/per-stock/COHR/financials.xlsx
+++ b/per-stock/COHR/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74822262784</v>
+        <v>76215214080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76162342912</v>
+        <v>77555294208</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>182.11906</v>
+        <v>185.50954</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47.48248</v>
+        <v>47.64339</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.333128</v>
+        <v>11.544115</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-197631744</v>
+        <v>-538236000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.45</v>
+        <v>389.57</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D44</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C44</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B44</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B45:E45)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B43:E43)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D38</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C38</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B38</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B39:E39)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B5:E5)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D4/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C4/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B4/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1716,13 +2196,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1731,6 +2211,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1741,25 +2222,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
@@ -1772,20 +2258,21 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-369651.884761</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-2104007.750554</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>18235350</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-29172150</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-15491490</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-1677985.903866</v>
-      </c>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1794,10 +2281,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.014505</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.143903</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.21</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0.21</v>
@@ -1806,8 +2293,9 @@
         <v>0.21</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.209199</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1816,20 +2304,21 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>387267000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>354565000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>311201000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>265367000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>287513000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>335164000</v>
-      </c>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1838,20 +2327,21 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-25484000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-14621000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>86835000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-138915000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-73769000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-8021000</v>
-      </c>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1860,20 +2350,21 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-25484000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-14621000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>86835000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-138915000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-73769000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-8021000</v>
-      </c>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1882,20 +2373,21 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>191402000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>146717000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>226349000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-95619000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>15711000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>103385000</v>
-      </c>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1904,20 +2396,21 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>132878000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>126019000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>122429000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>134823000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>146570000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>134461000</v>
-      </c>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1926,20 +2419,21 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1125696000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1062809000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>1002178000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>983287000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>970189000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>925314000</v>
-      </c>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1948,20 +2442,21 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>361783000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>339944000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>398036000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>126452000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>213744000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>327143000</v>
-      </c>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1970,20 +2465,21 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>228905000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>213925000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>275607000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-8371000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>67174000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>192682000</v>
-      </c>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1992,20 +2488,21 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-44558000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-45937000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-58721000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-55045000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-57284000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-64278000</v>
-      </c>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2014,20 +2511,21 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>44558000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>45937000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>58721000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>55045000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>57284000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>64278000</v>
-      </c>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2036,20 +2534,21 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>216516348.115239</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>159233992.249446</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>157749350</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>14123850</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>73988510</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>109728014.096134</v>
-      </c>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2058,20 +2557,21 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>191402000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>146717000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>226349000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-95619000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>15711000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>103385000</v>
-      </c>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2080,20 +2580,21 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>1579320000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>1487005000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1409139000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>1384458000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>1352359000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>1289778000</v>
-      </c>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2102,20 +2603,21 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>196367000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>192757000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>190684000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>155500000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>155200000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>159989000</v>
-      </c>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2124,20 +2626,21 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>190218000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>167512000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>156156000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>155500000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>155200000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>154767000</v>
-      </c>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2146,20 +2649,21 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-0.83</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>0.44</v>
-      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2168,20 +2672,21 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-0.83</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>0.46</v>
-      </c>
+      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2190,20 +2695,21 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>191402000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>146717000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>192870000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-128757000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-16982000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>71123000</v>
-      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2211,13 +2717,14 @@
           <t>Average Dilution Earnings</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n">
         <v>1623000</v>
       </c>
-      <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2228,20 +2735,21 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>191402000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>145094000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>192870000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-128757000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-16982000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>71123000</v>
-      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2249,19 +2757,20 @@
           <t>Preferred Stock Dividends</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n">
         <v>1623000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>33479000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>33138000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>32693000</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="G24" s="3" t="n">
         <v>32262000</v>
       </c>
     </row>
@@ -2272,20 +2781,21 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>191402000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>146717000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>226349000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-95619000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>15711000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>103385000</v>
-      </c>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2294,20 +2804,21 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>9729000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>2903000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>1153000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>2492000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>13946000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>1843000</v>
-      </c>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2316,20 +2827,21 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>181673000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>143814000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>225196000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-98111000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>1765000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>101542000</v>
-      </c>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2338,20 +2850,21 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>181673000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>143814000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>225196000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-98111000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>1765000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>101542000</v>
-      </c>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2360,20 +2873,21 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>2674000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>24174000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-8310000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>34695000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>8125000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>26862000</v>
-      </c>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2382,20 +2896,21 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>184347000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>167988000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>216886000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-63416000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>9890000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>128404000</v>
-      </c>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2404,20 +2919,21 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>2584000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>15301000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>103368000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-153349000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-78346000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>47795000</v>
-      </c>
+      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2426,20 +2942,21 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>28068000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>29922000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>16533000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-14434000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-4577000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>55816000</v>
-      </c>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2448,20 +2965,21 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-25484000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-14621000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>86835000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-138915000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-73769000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-8021000</v>
-      </c>
+      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2469,13 +2987,18 @@
           <t>Gain On Sale Of Business</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n">
+      <c r="B34" s="3" t="n">
+        <v>8922000</v>
+      </c>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n">
         <v>115211000</v>
       </c>
-      <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2483,15 +3006,16 @@
           <t>Write Off</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
         <v>11012000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>9100000</v>
       </c>
-      <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2502,20 +3026,21 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>34406000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>3609000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>19276000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>53927000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>73769000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>8021000</v>
-      </c>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2524,20 +3049,21 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-44558000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-45937000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-58721000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>-55045000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-57284000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-64278000</v>
-      </c>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2546,20 +3072,21 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>44558000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>45937000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>58721000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>55045000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>57284000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>64278000</v>
-      </c>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2568,20 +3095,21 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>226321000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>198624000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>172239000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>144978000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>145520000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>144887000</v>
-      </c>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2590,20 +3118,21 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>453624000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>424196000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>406961000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>401171000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>382170000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>364464000</v>
-      </c>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2612,20 +3141,21 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>185985000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>165708000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>154877000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>155739000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>150731000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>143852000</v>
-      </c>
+      <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2634,20 +3164,21 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>267639000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>258488000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>252084000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>245432000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>231439000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>220612000</v>
-      </c>
+      <c r="G42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2656,20 +3187,21 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>679945000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>622820000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>579200000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>546149000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>527690000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>509351000</v>
-      </c>
+      <c r="G43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2678,20 +3210,21 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>1125696000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>1062809000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>1002178000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>983287000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>970189000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>925314000</v>
-      </c>
+      <c r="G44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2700,20 +3233,21 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>1805641000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>1685629000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>1581378000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>1529436000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>1497879000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>1434665000</v>
-      </c>
+      <c r="G45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2722,27 +3256,28 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>1805641000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>1685629000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>1581378000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>1529436000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>1497879000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>1434665000</v>
-      </c>
+      <c r="G46" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4414,7 +4949,1939 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>16794638</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>16763485</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>16706280</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>16294119</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>16219804</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>195546098</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>187422356</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>156952622</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>155555206</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>155347444</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>212340736</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>204185841</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>173658902</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>171849325</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>171567248</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1601051000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2488127000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2455007000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2777721000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2841539000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>3425115000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3546525000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>3505852000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3893658000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>3944525000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>3316386000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1012441000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-1777813000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-2031317000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-2387855000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>13870764000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>11891162000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>9137984000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>9331435000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>9084419000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>4331759000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2442299000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2305980000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2132313000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2202853000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>3316386000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1012441000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>727489000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>451944000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>73705000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>231334000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>194659000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>198067000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>206737000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>212728000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>10676983000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>8539296000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>5830199000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>5644514000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>5352622000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Preferred Stock Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n">
+        <v>2505302000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2483261000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2461560000</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>2428867000</v>
+      </c>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>13861753000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>11784699000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>11594907000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>11626390000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>11541312000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>11015686000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>8888284000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>8687415000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>8481283000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>8168789000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>338703000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>348988000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>351914000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>353508000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>354607000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>10676983000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>8539296000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>8335501000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>8127775000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>7814182000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>241604000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>355348000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>339737000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>372037000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-11273000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>241604000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>355348000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>339737000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>372037000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-11273000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>419645000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>412680000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>405508000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>368065000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>363010000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1113740000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>922338000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>777244000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>584374000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>713135000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>9741284000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>7674290000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>7624028000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>7539429000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>7475330000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>9741284000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>7674290000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>5118726000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>5056168000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>5013770000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2505302000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2483261000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2461560000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6271015000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>6199433000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>6011430000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>6429653000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>6276036000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>4157571000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>4248345000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>4275455000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>4634812000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>4779032000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>188161000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>208054000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>229858000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>259318000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>208084000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Preferred Securities Outside Stock Equity</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n">
+        <v>2396605000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>605750000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>643250000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>629504000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>711717000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>673815000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>605750000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>643250000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>629504000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>711717000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>673815000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>3363660000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>3397041000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>3416093000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>3663777000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>3897133000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>178890000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>151638000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>156687000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>165162000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>170003000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>3184770000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>3245403000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>3259406000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>3498615000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>3727130000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>2113444000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1951088000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1735975000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1794841000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1497004000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n">
+        <v>57394000</v>
+      </c>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n">
+        <v>62967000</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n">
+        <v>62967000</v>
+      </c>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>61455000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>149484000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>89759000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>229881000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>47392000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>52444000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>43021000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>41380000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>41575000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>42725000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>9011000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>106463000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>48379000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>188306000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>4667000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>9011000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>106463000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>48379000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>188306000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>4667000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>276580000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>243088000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>210444000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>258650000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>242332000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Current Provisions</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n">
+        <v>32754000</v>
+      </c>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1775409000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1558516000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1435772000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1153195000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1207280000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>332785000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>312033000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>317612000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>182449000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>312615000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1442624000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1246483000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1118160000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>970746000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>894665000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>99249000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>127977000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>164271000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>123762000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>117334000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>99249000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>127977000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>164271000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>123762000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>117334000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>1343375000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1118506000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>953889000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>846984000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>777331000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>17286701000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>15087717000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>14698845000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>14910936000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>14444825000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>10841498000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>10694330000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>10656890000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>10983782000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>10744968000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>988709000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>981427000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1050591000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1377037000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1015500000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>72111000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>69091000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>53934000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>53407000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>52555000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>72111000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>69091000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>53934000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>53407000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>52555000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>7360597000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>7526855000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>7608012000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>7675831000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>7740477000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>2958194000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>3064069000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>3133179000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>3204747000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>3282517000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>4402403000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>4462786000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>4474833000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>4471084000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>4457960000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>2420081000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>2116957000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1944353000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1877507000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1936436000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>-1743514000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>-1712980000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>-1665292000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-1615252000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>-1668399000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>4163595000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>3829937000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>3609645000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>3492759000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>3604835000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>483642000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>348182000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>313646000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>363129000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>522821000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>2661452000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>2486524000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>2317545000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>2188509000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>2188137000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>956645000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>935704000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>918841000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>881578000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>802429000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>61856000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>59527000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>59613000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>59543000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>66448000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>6445203000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>4393387000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>4041955000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>3927154000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>3699857000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>625262000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>547593000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>461980000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>551597000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>364070000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>42033000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>35451000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>22549000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>8897000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>19064000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>2126823000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1847907000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1632605000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>1437636000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1391525000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>275251000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>265939000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>211509000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>218594000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>225057000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>1238182000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1097374000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>952945000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>824360000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>745885000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>613390000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>484594000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>468151000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>394682000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>420583000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>1233355000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>1098697000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>1072043000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1019824000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>1034940000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>45495000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>44086000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>44812000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>55773000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>24912000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>1187860000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>1054611000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>1027231000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>964051000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1010028000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>-13066000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>-12856000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>-13339000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-12189000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>-10167000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>1200926000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>1067467000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>1040570000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>976240000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>1020195000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>2417730000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>863739000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>852778000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>909200000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>890258000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>825000000</v>
+      </c>
+      <c r="C80" s="3" t="n"/>
+      <c r="D80" s="3" t="n"/>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>1592730000</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>863739000</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>852778000</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>909200000</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>890258000</v>
+      </c>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5686,13 +8153,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5701,6 +8168,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5711,25 +8179,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
@@ -5742,20 +8215,21 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-383481000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-95698000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-57991000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-1066000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>51138000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>81696000</v>
-      </c>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5764,20 +8238,21 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-475833000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-182908000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-1727851000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-68493000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-169944000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-132351000</v>
-      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5786,20 +8261,21 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>315234000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>224669000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>1342175000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>17867000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>35862000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5808,20 +8284,21 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-289684000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-153598000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-103946000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-131350000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-111819000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-105683000</v>
-      </c>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5830,20 +8307,21 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>32349000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>62027000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>40996000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>68905000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>45314000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>79051000</v>
-      </c>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5852,20 +8330,21 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>67304000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>51170000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>49375000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>59065000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>41417000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>32468000</v>
-      </c>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5874,20 +8353,21 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>2225778000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>1528796000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>1552900000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>1632913000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>1626030000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>1668642000</v>
-      </c>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5896,20 +8376,21 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1528796000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1552900000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>1632913000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>1626030000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>1668642000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>1782458000</v>
-      </c>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5918,20 +8399,21 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-14162000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>13469000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-1280000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>72528000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>26177000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-54326000</v>
-      </c>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5940,20 +8422,21 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>711144000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-37573000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-78733000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-65645000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-68789000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-59490000</v>
-      </c>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5962,20 +8445,21 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>1854342000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>43058000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-421486000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-65238000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-120015000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-140810000</v>
-      </c>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5984,20 +8468,21 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>1854342000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>43058000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-421486000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-65238000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-120015000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-140810000</v>
-      </c>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6006,20 +8491,21 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-6754000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-7512000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-45650000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-5282000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-4161000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-13288000</v>
-      </c>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6028,20 +8514,21 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>21695000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>8809000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>21278000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>2108000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>18228000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>4829000</v>
-      </c>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6053,13 +8540,18 @@
         <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>-11438000</v>
       </c>
-      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6068,20 +8560,21 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-160599000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>41761000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-385676000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-50626000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-134082000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-132351000</v>
-      </c>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6090,20 +8583,21 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-160599000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>41761000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-385676000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-50626000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-134082000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-132351000</v>
-      </c>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6112,20 +8606,21 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-475833000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-182908000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-1727851000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-68493000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-169944000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-132351000</v>
-      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6134,20 +8629,21 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>315234000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>224669000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>1342175000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>17867000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>35862000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6156,20 +8652,21 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-1049401000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-138531000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>296798000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-130691000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-111731000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-106059000</v>
-      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6178,20 +8675,21 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-1049401000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-138531000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>296798000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-130691000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-111731000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-106059000</v>
-      </c>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6200,661 +8698,729 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-3502000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-1499000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-18000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>659000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>88000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-376000</v>
-      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Net Business Purchase And Sale</t>
+          <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-14965000</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>400762000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-807704000</v>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sale Of Business</t>
+          <t>Sale Of Investment</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-14965000</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>400762000</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>17296000</v>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Net PPE Purchase And Sale</t>
+          <t>Net Business Purchase And Sale</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-153598000</v>
+        <v>51489000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-103946000</v>
+        <v>-14965000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-131350000</v>
+        <v>400762000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-111819000</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-105683000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Purchase Of PPE</t>
+          <t>Sale Of Business</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-153598000</v>
+        <v>51489000</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-103946000</v>
+        <v>-14965000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-131350000</v>
+        <v>400762000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-111819000</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-105683000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>57900000</v>
+        <v>-289684000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>45955000</v>
+        <v>-153598000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>130284000</v>
+        <v>-103946000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>162957000</v>
+        <v>-131350000</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>187379000</v>
-      </c>
+        <v>-111819000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
+          <t>Purchase Of PPE</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>57900000</v>
+        <v>-289684000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>45955000</v>
+        <v>-153598000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>130284000</v>
+        <v>-103946000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>162957000</v>
+        <v>-131350000</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>187379000</v>
-      </c>
+        <v>-111819000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-259376000</v>
+        <v>-93797000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-158602000</v>
+        <v>57900000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-70969000</v>
+        <v>45955000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-44020000</v>
+        <v>130284000</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-46302000</v>
-      </c>
+        <v>162957000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Change In Other Working Capital</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-132578000</v>
+        <v>-93797000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>21789000</v>
+        <v>57900000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-50307000</v>
+        <v>45955000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>33783000</v>
+        <v>130284000</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>23494000</v>
-      </c>
+        <v>162957000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Change In Payables And Accrued Expense</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>100214000</v>
+        <v>-392293000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>105357000</v>
+        <v>-259376000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>89094000</v>
+        <v>-158602000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>80243000</v>
+        <v>-70969000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3376000</v>
-      </c>
+        <v>-44020000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Change In Payable</t>
+          <t>Change In Other Working Capital</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>100214000</v>
+        <v>-124460000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>105357000</v>
+        <v>-132578000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>89094000</v>
+        <v>21789000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>80243000</v>
+        <v>-50307000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3376000</v>
-      </c>
+        <v>33783000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Change In Account Payable</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>144095000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>100214000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>105357000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>89094000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>80243000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>3376000</v>
-      </c>
+      <c r="G34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Change In Inventory</t>
+          <t>Change In Payable</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-202253000</v>
+        <v>144095000</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-219120000</v>
+        <v>100214000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-105427000</v>
+        <v>105357000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-30780000</v>
+        <v>89094000</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-11740000</v>
-      </c>
+        <v>80243000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Change In Account Payable</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-24759000</v>
+        <v>144095000</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-66628000</v>
+        <v>100214000</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-4329000</v>
+        <v>105357000</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-127266000</v>
+        <v>89094000</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-61432000</v>
-      </c>
+        <v>80243000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Changes In Account Receivables</t>
+          <t>Change In Inventory</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-24759000</v>
+        <v>-278047000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-66628000</v>
+        <v>-202253000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-4329000</v>
+        <v>-219120000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-127266000</v>
+        <v>-105427000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-61432000</v>
-      </c>
+        <v>-30780000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>13183000</v>
+        <v>-133881000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>19658000</v>
+        <v>-24759000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>102023000</v>
+        <v>-66628000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>29875000</v>
+        <v>-4329000</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>4952000</v>
-      </c>
+        <v>-127266000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Changes In Account Receivables</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>42768000</v>
+        <v>-133881000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>44134000</v>
+        <v>-24759000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>43590000</v>
+        <v>-66628000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>40960000</v>
+        <v>-4329000</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>40729000</v>
-      </c>
+        <v>-127266000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deferred Tax</t>
+          <t>Other Non Cash Items</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>10601000</v>
+        <v>23761000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-83665000</v>
+        <v>13183000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-7333000</v>
+        <v>19658000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-28483000</v>
+        <v>102023000</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-16963000</v>
-      </c>
+        <v>29875000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deferred Income Tax</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>10601000</v>
+        <v>49147000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-83665000</v>
+        <v>42768000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-7333000</v>
+        <v>44134000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-28483000</v>
+        <v>43590000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-16963000</v>
-      </c>
+        <v>40960000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Deferred Tax</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>126019000</v>
+        <v>-64971000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>122429000</v>
+        <v>10601000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>134823000</v>
+        <v>-83665000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>146570000</v>
+        <v>-7333000</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>134461000</v>
-      </c>
+        <v>-28483000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Deferred Income Tax</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>126019000</v>
+        <v>-64971000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>122429000</v>
+        <v>10601000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>134823000</v>
+        <v>-83665000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>146570000</v>
+        <v>-7333000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>134461000</v>
-      </c>
+        <v>-28483000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Amortization Cash Flow</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>70508000</v>
+        <v>132878000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>69446000</v>
+        <v>126019000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>72047000</v>
+        <v>122429000</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>87163000</v>
+        <v>134823000</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>71716000</v>
-      </c>
+        <v>146570000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>70508000</v>
+        <v>132878000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>69446000</v>
+        <v>126019000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>72047000</v>
+        <v>122429000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>87163000</v>
+        <v>134823000</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>71716000</v>
-      </c>
+        <v>146570000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Amortization Cash Flow</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>55511000</v>
+        <v>70469000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>52983000</v>
+        <v>70508000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>62776000</v>
+        <v>69446000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>59407000</v>
+        <v>72047000</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>62745000</v>
-      </c>
+        <v>87163000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Amortization Of Intangibles</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-19109000</v>
+        <v>70469000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>-123195000</v>
+        <v>70508000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>26261000</v>
+        <v>69446000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>16290000</v>
+        <v>72047000</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-31040000</v>
-      </c>
+        <v>87163000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Earnings Losses From Equity Investments</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-61000</v>
+        <v>62409000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>-215000</v>
+        <v>55511000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>-690000</v>
+        <v>52983000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>-125000</v>
+        <v>62776000</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>-109000</v>
-      </c>
+        <v>59407000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Net Foreign Currency Exchange Gain Loss</t>
+          <t>Operating Gains Losses</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-4257000</v>
+        <v>-23992000</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>-4226000</v>
+        <v>-19109000</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>26281000</v>
+        <v>-123195000</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>16370000</v>
+        <v>26261000</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-31020000</v>
-      </c>
+        <v>16290000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Gain Loss On Sale Of PPE</t>
+          <t>Earnings Losses From Equity Investments</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>21000</v>
+        <v>-18000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>127000</v>
+        <v>-61000</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>670000</v>
+        <v>-215000</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>45000</v>
+        <v>-690000</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>89000</v>
-      </c>
+        <v>-125000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gain Loss On Sale Of Business</t>
+          <t>Net Foreign Currency Exchange Gain Loss</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>6726000</v>
+        <v>-1735000</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>-121937000</v>
-      </c>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
+        <v>-4257000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>-4226000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>26281000</v>
+      </c>
       <c r="F51" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>16370000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Gain Loss On Sale Of PPE</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>777000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>21000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>127000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>670000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gain Loss On Sale Of Business</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>-44554000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>6726000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>-121937000</v>
+      </c>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B54" s="3" t="n">
+        <v>181673000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>143814000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>225196000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>-98111000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>1765000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>101542000</v>
-      </c>
+      <c r="G54" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
